--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131042260</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127728</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/210643</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/295736</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1465603</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1625854</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1731159</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106835459</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106835456</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106835462</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76895824</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,6 +2027,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106835457</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2075,6 +2140,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106835461</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746892</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2289,6 +2364,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109929383</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121352322</t>
         </is>
       </c>
     </row>
@@ -2510,6 +2595,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109739687</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2630,6 +2720,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59941691</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2732,6 +2827,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571869</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2829,6 +2929,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569588</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2936,6 +3041,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125566159</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3043,6 +3153,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125566395</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3150,6 +3265,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569639</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3257,6 +3377,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125569912</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3354,6 +3479,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126177922</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3451,6 +3581,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694310</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3548,6 +3683,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175532</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3645,6 +3785,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126175887</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3742,6 +3887,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694160</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3839,6 +3989,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694146</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3936,6 +4091,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103694147</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4066,6 +4226,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324892</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4186,6 +4351,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669930</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4304,6 +4474,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669932</t>
         </is>
       </c>
     </row>
@@ -4411,6 +4586,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121176857</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4528,6 +4708,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125302423</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4663,6 +4848,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324694</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4793,6 +4983,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324686</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4928,6 +5123,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324718</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5058,6 +5258,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324772</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5178,6 +5383,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669651</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5298,6 +5508,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669653</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5421,6 +5636,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325346</t>
         </is>
       </c>
     </row>
@@ -5538,6 +5758,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126319593</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5668,6 +5893,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325345</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5788,6 +6018,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669657</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5908,6 +6143,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669658</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6023,6 +6263,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669661</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6143,6 +6388,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669662</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6256,6 +6506,11 @@
       <c r="AY51" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669656</t>
         </is>
       </c>
     </row>
@@ -6369,6 +6624,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126319604</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6484,6 +6744,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669660</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6610,6 +6875,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55256899</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6730,6 +7000,11 @@
       <c r="AY55" t="inlineStr">
         <is>
           <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55256862</t>
         </is>
       </c>
     </row>
@@ -6853,6 +7128,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116928181</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6974,6 +7254,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116928221</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7092,6 +7377,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99426318</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7208,6 +7498,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114364480</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7305,6 +7600,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980184</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7402,6 +7702,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980000</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7512,6 +7817,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120446237</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7624,6 +7934,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125181592</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7738,6 +8053,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120540898</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7845,6 +8165,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128960340</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7946,6 +8271,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155315</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8047,6 +8377,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155316</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8153,6 +8488,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155314</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8265,6 +8605,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125123246</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8367,6 +8712,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124421672</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8468,6 +8818,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155317</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8567,6 +8922,11 @@
       <c r="AY72" t="inlineStr">
         <is>
           <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130156222</t>
         </is>
       </c>
     </row>
@@ -8680,6 +9040,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126412211</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8792,6 +9157,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133593374</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8899,6 +9269,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129730828</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9015,6 +9390,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126201679</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9136,6 +9516,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669910</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9266,6 +9651,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284491</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9396,6 +9786,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325626</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9493,6 +9888,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1935699</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9599,6 +9999,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1935700</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9705,6 +10110,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1935701</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9824,6 +10234,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85250968</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9947,8 +10362,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81919158</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ84"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10242,64 +10242,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>81919158</v>
+        <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>57144</v>
+        <v>89431</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102613</v>
+        <v>510</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Armsjötorpet vägen nerströms , Mpd</t>
+          <t>Lappmon, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>626692</v>
+        <v>603206</v>
       </c>
       <c r="R84" t="n">
-        <v>6893681</v>
+        <v>6897616</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10318,27 +10302,27 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>Njurunda</t>
+          <t>Attmar</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2020-01-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10353,16 +10337,144 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Rode Nordin</t>
+          <t>Sara Widell</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Rode Nordin, Bruno Nordin</t>
+          <t>Sara Widell</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136130914</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>81919158</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Armsjötorpet vägen nerströms , Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>626692</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6893681</v>
+      </c>
+      <c r="S85" t="n">
+        <v>8</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2020-01-26</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81919158</t>
         </is>
@@ -10453,6 +10565,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96460</v>
+        <v>96631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96632</v>
+        <v>96633</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96633</v>
+        <v>96639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96639</v>
+        <v>96640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96640</v>
+        <v>96651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89440</v>
+        <v>89446</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96651</v>
+        <v>96664</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89446</v>
+        <v>89453</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89453</v>
+        <v>89454</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96665</v>
+        <v>96678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89454</v>
+        <v>89467</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/S 308-2024 artfynd.xlsx
+++ b/artfynd/S 308-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>76895824</v>
       </c>
       <c r="B12" t="n">
-        <v>96678</v>
+        <v>96679</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>136130914</v>
       </c>
       <c r="B84" t="n">
-        <v>89467</v>
+        <v>89468</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
